--- a/20260928_チェングロウス_LINE友だち追加_数値感（仮置き）.xlsx
+++ b/20260928_チェングロウス_LINE友だち追加_数値感（仮置き）.xlsx
@@ -634,14 +634,24 @@
         <v>200000</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>広告以外の流入UU（自然流入・求人ボックス等）</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>1000</v>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>UU（基準・月）＝広告費÷クリック単価</t>
+          <t>UU（基準・月）＝広告費÷クリック単価＋広告以外の流入</t>
         </is>
       </c>
       <c r="C15" s="6">
-        <f>$C$4/$C$5</f>
+        <f>$C$4/$C$5+$C$14</f>
         <v/>
       </c>
     </row>

--- a/20260928_チェングロウス_LINE友だち追加_数値感（仮置き）.xlsx
+++ b/20260928_チェングロウス_LINE友だち追加_数値感（仮置き）.xlsx
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="15">

--- a/20260928_チェングロウス_LINE友だち追加_数値感（仮置き）.xlsx
+++ b/20260928_チェングロウス_LINE友だち追加_数値感（仮置き）.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -139,6 +139,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -504,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -518,6 +519,8 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -711,6 +714,16 @@
           <t>友だち追加（累計）</t>
         </is>
       </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>ブロック率</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>有効友だち（累計）</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -755,6 +768,13 @@
         <f>J18</f>
         <v/>
       </c>
+      <c r="L18" s="18" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="M18" s="14">
+        <f>ROUND(J18*(1-L18),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -799,6 +819,13 @@
         <f>K18+J19</f>
         <v/>
       </c>
+      <c r="L19" s="18" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="M19" s="14">
+        <f>M18+ROUND(J19*(1-L19),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -843,6 +870,13 @@
         <f>K19+J20</f>
         <v/>
       </c>
+      <c r="L20" s="18" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="M20" s="14">
+        <f>M19+ROUND(J20*(1-L20),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -887,6 +921,13 @@
         <f>K20+J21</f>
         <v/>
       </c>
+      <c r="L21" s="18" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="M21" s="14">
+        <f>M20+ROUND(J21*(1-L21),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -931,6 +972,13 @@
         <f>K21+J22</f>
         <v/>
       </c>
+      <c r="L22" s="18" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="M22" s="14">
+        <f>M21+ROUND(J22*(1-L22),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -975,6 +1023,13 @@
         <f>K22+J23</f>
         <v/>
       </c>
+      <c r="L23" s="18" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="M23" s="14">
+        <f>M22+ROUND(J23*(1-L23),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -1019,6 +1074,13 @@
         <f>K23+J24</f>
         <v/>
       </c>
+      <c r="L24" s="18" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="M24" s="14">
+        <f>M23+ROUND(J24*(1-L24),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -1063,6 +1125,13 @@
         <f>K24+J25</f>
         <v/>
       </c>
+      <c r="L25" s="18" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="M25" s="14">
+        <f>M24+ROUND(J25*(1-L25),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -1107,6 +1176,13 @@
         <f>K25+J26</f>
         <v/>
       </c>
+      <c r="L26" s="18" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="M26" s="14">
+        <f>M25+ROUND(J26*(1-L26),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -1151,6 +1227,13 @@
         <f>K26+J27</f>
         <v/>
       </c>
+      <c r="L27" s="18" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="M27" s="14">
+        <f>M26+ROUND(J27*(1-L27),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -1195,6 +1278,13 @@
         <f>K27+J28</f>
         <v/>
       </c>
+      <c r="L28" s="18" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="M28" s="14">
+        <f>M27+ROUND(J28*(1-L28),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -1239,6 +1329,13 @@
         <f>K28+J29</f>
         <v/>
       </c>
+      <c r="L29" s="18" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="M29" s="14">
+        <f>M28+ROUND(J29*(1-L29),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
@@ -1295,6 +1392,13 @@
       <c r="A37" s="17" t="inlineStr">
         <is>
           <t>通知メッセージ経由（Indeed・求人ボックスの応募者）は含まない（応募数が不明のため・上振れ要素）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>ブロック率：初月40%前後（求人は用済み型で38〜42%）から、出し分け配信で徐々に下げ、翌3月に30%前後（定義テキストの目標「30%以内」）。12月は配信が止まりがちで一時悪化</t>
         </is>
       </c>
     </row>
